--- a/outputs/9726.xlsx
+++ b/outputs/9726.xlsx
@@ -1,65 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
+  <si>
+    <t xml:space="preserve">Student ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visit number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visit date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submission date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1458</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d\-mmm\-yy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="d\-mmm\-yy"/>
   </numFmts>
   <fonts count="4">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -67,119 +96,61 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellXfs count="5">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -356,158 +327,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="10.29" customWidth="1" style="4" min="1" max="1"/>
-    <col width="12.43" customWidth="1" style="4" min="2" max="3"/>
-    <col width="10.29" customWidth="1" style="4" min="4" max="4"/>
-    <col width="12.72" customWidth="1" style="4" min="5" max="5"/>
-    <col width="10.29" customWidth="1" style="4" min="8" max="8"/>
-    <col width="15.72" customWidth="1" style="4" min="9" max="9"/>
-    <col width="10.14" customWidth="1" style="4" min="10" max="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="12.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Student ID</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Visit number</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Visit date</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>Student ID</t>
-        </is>
-      </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>Submission date</t>
-        </is>
-      </c>
-      <c r="J1" s="6" t="inlineStr">
-        <is>
-          <t>Visit date</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="5">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>A1253</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>42504</v>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>A1253</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="n">
+      <c r="H2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="3" t="n">
         <v>42542</v>
       </c>
-      <c r="J2" s="7">
-        <f>_xlfn.MAXIFS($C$2:$C$7,$A$2:$A$7,H2,$C$2:$C$7,"&lt;"&amp;I2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="5">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>A1253</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
+      <c r="J2" s="3" t="n">
+        <f aca="false" t="array" ref="J2:J2">MAX(IF(A2:A7=H2,IF(C2:C7&lt;I2,C2:C7)))</f>
+        <v>42533</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="3" t="n">
         <v>42521</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>A1253</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="3" t="n">
         <v>42533</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>A1253</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="7" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>42542</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>A1458</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="3" t="n">
         <v>42490</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>A1458</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="3" t="n">
         <v>42494</v>
       </c>
-      <c r="J7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="5">
-      <c r="J8" s="8" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="5">
-      <c r="C19" s="4">
-        <f>COUNT(4,5,6,7)</f>
-        <v/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J8" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="1" t="n">
+        <f aca="false">COUNT(4,5,6,7)</f>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/outputs/9726.xlsx
+++ b/outputs/9726.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="153222"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\413343\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10695"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="152511"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -22,54 +26,35 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
   <si>
-    <t xml:space="preserve">Student ID</t>
+    <t>Student ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Visit number</t>
+    <t>A1253</t>
   </si>
   <si>
-    <t xml:space="preserve">Visit date</t>
+    <t>Visit date</t>
   </si>
   <si>
-    <t xml:space="preserve">Submission date</t>
+    <t>Visit number</t>
   </si>
   <si>
-    <t xml:space="preserve">A1253</t>
+    <t>Submission date</t>
   </si>
   <si>
-    <t xml:space="preserve">A1458</t>
+    <t>A1458</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="d\-mmm\-yy"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -81,88 +66,63 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -197,55 +157,119 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -253,24 +277,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -283,7 +316,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -293,13 +332,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -307,6 +348,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -314,41 +356,45 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="12.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.14"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -357,105 +403,102 @@
         <v>0</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>42504</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
+        <v>42542</v>
+      </c>
+      <c r="J2" s="3">
+        <f t="array" ref="J2">INDEX(C2:C7,MATCH(TRUE,IF(H2=$A$2:$A$7,INDEX($C$2:$C$7&lt;I2,0)),0))</f>
+        <v>42504</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>42521</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3">
+        <v>42533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>42504</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="C5" s="3">
         <v>42542</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <f aca="false" t="array" ref="J2:J2">MAX(IF(A2:A7=H2,IF(C2:C7&lt;I2,C2:C7)))</f>
-        <v>42533</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>42521</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>42533</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>42542</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
         <v>42490</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="2">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="3">
         <v>42494</v>
       </c>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J8" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="1" t="n">
-        <f aca="false">COUNT(4,5,6,7)</f>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="1"/>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <f>COUNT(4,5,6,7)</f>
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <sortState ref="B2:E5">
+    <sortCondition ref="E2:E5"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>